--- a/artifacts/program-spec.xlsx
+++ b/artifacts/program-spec.xlsx
@@ -670,7 +670,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>클라이언트가 보낸 SQL 이 이 시스템이 다룰 수 있는 모양인지 검사하고, 나눌 기준이 되는 IN 절을 찾아
+          <t xml:space="preserve">클라이언트가 보낸 SQL 이 이 시스템이 다룰 수 있는 모양인지 검사하고, 나눌 기준이 되는 IN 절을 찾아
 내는 프로그램이다. 검사는 글자를 훑는 것이 아니라 sqlglot 으로 SQL 을 구문 트리로 만들어서 한다.
 문자열 검사는 주석이나 따옴표에 쉽게 속지만 트리는 속지 않기 때문이다.</t>
         </is>
@@ -710,7 +710,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>검증을 통과한 SELECT 하나를 여러 개의 SELECT 로 나누는 프로그램이다. 이 시스템이 빨라지는 이유가
+          <t xml:space="preserve">검증을 통과한 SELECT 하나를 여러 개의 SELECT 로 나누는 프로그램이다. 이 시스템이 빨라지는 이유가
 바로 여기에 있다. 파티션 컬럼의 IN 목록에 값이 100개 있고 4조각으로 나누라고 하면, 값을 25개씩
 나눠 가진 SELECT 네 개를 만든다.</t>
         </is>
@@ -829,8 +829,8 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>접수된 작업 하나를 실제로 끝까지 몰고 가는 프로그램이며 이 시스템에서 가장 복잡한 자리다. 조각들을
-executor 들에게 나눠 보내고, 진행 상황을 물어보며 기다리고, 실패하면 다른 executor 로 넘기고,
+          <t xml:space="preserve">접수된 작업 하나를 실제로 끝까지 몰고 가는 프로그램이며 이 시스템에서 가장 복잡한 자리다. 조각들을
+executor 들에게 나눠 보내고, 진행 상황을 물어보며 기다리고, 미접수가 확실한 실패만 다른 executor 로 넘기고,
 마지막에 작업 전체의 상태를 판정한다.</t>
         </is>
       </c>
@@ -987,7 +987,7 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>coordinator 가 보낸 조각 하나를 받아 실제로 실행하고, 그 진행 상태를 물어보면 알려 주는
+          <t xml:space="preserve">coordinator 가 보낸 조각 하나를 받아 실제로 실행하고, 그 진행 상태를 물어보면 알려 주는
 프로그램이다. executor 쪽의 입구에 해당한다.</t>
         </is>
       </c>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>coordinator 가 보낸 조각 하나를 받아 실제로 실행하고, 그 진행 상태를 물어보면 알려 주는
+          <t xml:space="preserve">coordinator 가 보낸 조각 하나를 받아 실제로 실행하고, 그 진행 상태를 물어보면 알려 주는
 프로그램이다. executor 쪽의 입구에 해당한다.
 접수와 실행을 분리한 것이 핵심이다. 요청을 받으면 곧바로 202 를 돌려주고 실제 실행은
 백그라운드로 넘긴다. 이관은 몇 시간이 걸릴 수 있어서 응답을 붙들고 있을 수 없기 때문이다.
@@ -1390,15 +1390,19 @@
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>1. 접수
-조각을 받아 저장하고 곧바로 응답한다. 이때 대기 단계를 열어 두어 슬롯을 기다린 시간이 측정되게 한다.
+          <t xml:space="preserve">1. 접수
+보유 중인 task_id에 같은 요청이 오면 현재 상태를 반환하고, 본문이 다르면 409로 거절한다. 새 요청은 await 전에 task_id와 본문을 선점한다. 대기 시간을 측정하고 이력 저장과 실행은 응답 연결과 독립된 백그라운드에서 수행한다. 멱등 정보는 executor 프로세스 수명 동안 유지된다.
     FUNCTION CREATE_TASK(요청):
+        IF 요청.task_id IN tasks THEN
+            IF 저장한본문 != 요청본문 THEN THROW 409 TASK_ID_CONFLICT
+            RETURN 202 {task_id, status:현재상태}
+        IF 드레이닝중 THEN THROW 503
         task = NEW Task(요청의 모든 필드)
         task.status = QUEUED
         task.on_stage("QUEUE_WAIT", "start")     // 슬롯 대기 시작
         tasks[task.task_id] = task
-        HISTORY.RECORD(task)
-        백그라운드 시작: RUN_WITH_SEMAPHORE(task)
+        task_requests[task.task_id] = 요청본문
+        백그라운드 시작: HISTORY.RECORD(task) 후 RUN_WITH_SEMAPHORE(task)
         RETURN 202 {task_id, status:"QUEUED"}
 2. 동시 실행 제한
 이 executor 가 한 번에 처리할 조각 수를 세마포어로 제한한다. 제한이 없으면 원본과 목적지 양쪽에 연결이 몰려 오히려 느려진다.
@@ -2251,7 +2255,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>클라이언트가 보낸 SQL 이 이 시스템이 다룰 수 있는 모양인지 검사하고, 나눌 기준이 되는 IN 절을 찾아
+          <t xml:space="preserve">클라이언트가 보낸 SQL 이 이 시스템이 다룰 수 있는 모양인지 검사하고, 나눌 기준이 되는 IN 절을 찾아
 내는 프로그램이다. 검사는 글자를 훑는 것이 아니라 sqlglot 으로 SQL 을 구문 트리로 만들어서 한다.
 문자열 검사는 주석이나 따옴표에 쉽게 속지만 트리는 속지 않기 때문이다.
 검사의 목적은 두 가지다. 하나는 안전이다. SELECT 가 아닌 문장이나 세미콜론으로 이어 붙인 여러
@@ -2263,7 +2267,7 @@
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>1. 입력 확인
+          <t xml:space="preserve">1. 입력 확인
 빈 쿼리와 빈 파티션 컬럼을 먼저 거른다. 뒤 단계에서 엉뚱한 오류로 번지는 것을 막기 위해서다.
     IF sql 이 비었음 THEN THROW PARSE_ERROR
     IF partition_column 이 비었음 THEN THROW MISSING_PARTITION_COLUMN
@@ -2293,12 +2297,13 @@
     in_node = FIND_PARTITION_IN(stmt, partition_column)
     IF in_node == NULL THEN THROW NO_PARTITION_IN_CLAUSE
 6. IN 절 자체의 제약 검사
-찾은 IN 이 나눌 수 있는 모양인지 본다. 세 가지 모두 나눌 수 없는 경우다.
+찾은 IN은 해당 WHERE의 필수 양의 조건이어야 한다. OR·부정·값 표현식 안에 있으면 거절한다.
     IF in_node 가 NOT IN 임        THEN THROW NEGATED_IN
+    IF 필수 WHERE 조건이 아님      THEN THROW UNSAFE_PARTITION_PREDICATE
     IF in_node 값목록이 비었음      THEN THROW EMPTY_IN_LIST
     IF in_node 안에 서브쿼리 있음   THEN THROW SUBQUERY_IN_CLAUSE
 7. 파싱 결과 반환
-원문과 트리, 컬럼과 방언을 함께 담아 돌려준다. 분할기가 원문 포맷을 보존한 채 값만 바꾸려면 원문과 트리가 모두 필요하다.
+중복 값을 입력 순서대로 제거하고 원문과 트리, 컬럼과 방언을 함께 담아 돌려준다. 분할기가 원문 포맷을 보존한 채 값만 바꾸려면 원문과 트리가 모두 필요하다.
     RETURN ParsedQuery(sql=원문, expression=stmt,
                        partition_column, dialect, in_values=in_node 의 값들)
 ---</t>
@@ -2404,7 +2409,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>검증을 통과한 SELECT 하나를 여러 개의 SELECT 로 나누는 프로그램이다. 이 시스템이 빨라지는 이유가
+          <t xml:space="preserve">검증을 통과한 SELECT 하나를 여러 개의 SELECT 로 나누는 프로그램이다. 이 시스템이 빨라지는 이유가
 바로 여기에 있다. 파티션 컬럼의 IN 목록에 값이 100개 있고 4조각으로 나누라고 하면, 값을 25개씩
 나눠 가진 SELECT 네 개를 만든다.
 나눌 때 원문 포맷을 보존한다는 점이 이 프로그램의 특징이다. 구문 트리를 다시 문자열로 만들면
@@ -2415,7 +2420,7 @@
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>1. 값 목록 확보
+          <t xml:space="preserve">1. 값 목록 확보
 파싱 결과에서 IN 노드를 다시 찾아 값 표현식 목록을 꺼낸다.
     src_in = FIND_PARTITION_IN(parsed.expression, parsed.partition_column)
     value_exprs = src_in 의 값 표현식 목록
@@ -2429,8 +2434,8 @@
         앞에서부터 연속 구간으로 자르되, 나머지 rem 개는 앞쪽 버킷에 하나씩 더 준다
     buckets = 빈 버킷을 제거한 결과
 3. 원문에서 값 구간 찾기
-원문 문자열에서 값 목록이 시작하고 끝나는 위치를 한 번만 계산한다. 버킷마다 같은 구간을 쓰므로 반복문 밖에서 구한다.
-    span = VALUE_SPAN(parsed.sql, partition_column)   // (시작, 끝) 또는 NULL
+AST가 선택한 컬럼의 원문 위치와 SQL 토큰으로 값 목록의 시작·끝을 계산한다. 문자열·주석 안의 IN과 괄호는 구문으로 취급하지 않는다. 버킷마다 같은 구간을 쓰므로 반복문 밖에서 구한다.
+    span = VALUE_SPAN(parsed.sql, src_in, parsed.dialect)   // (시작, 끝) 또는 NULL
     IF span == NULL THEN
         로그: 포맷 보존 실패 → AST 재직렬화로 폴백
 4. 버킷마다 sub-query 생성
@@ -2863,8 +2868,8 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>접수된 작업 하나를 실제로 끝까지 몰고 가는 프로그램이며 이 시스템에서 가장 복잡한 자리다. 조각들을
-executor 들에게 나눠 보내고, 진행 상황을 물어보며 기다리고, 실패하면 다른 executor 로 넘기고,
+          <t xml:space="preserve">접수된 작업 하나를 실제로 끝까지 몰고 가는 프로그램이며 이 시스템에서 가장 복잡한 자리다. 조각들을
+executor 들에게 나눠 보내고, 진행 상황을 물어보며 기다리고, 미접수가 확실한 실패만 다른 executor 로 넘기고,
 마지막에 작업 전체의 상태를 판정한다.
 데이터는 여기를 지나가지 않는다. coordinator 는 "이 SQL 을 실행해 저 테이블에 넣어라"라고 시키고
 "몇 건 넣었다"는 답만 받는다. 수억 건의 행은 executor 와 데이터베이스 사이에서만 흐른다.
@@ -2874,7 +2879,7 @@
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>1. PENDING 으로 표시하고 슬롯 대기
+          <t xml:space="preserve">1. PENDING 으로 표시하고 슬롯 대기
 먼저 대기 상태로 저장한다. 슬롯이 없으면 여기서 기다리며, 그동안 조회하는 쪽에는 PENDING 으로 보인다.
     job.status = PENDING
     STORE.SAVE(job)
@@ -2917,31 +2922,21 @@
             FINALLY:
                 예약해제: RELEASE(task.executor_url)
 6. 조각 하나의 전송·재시도·폴링
-조각을 후보 executor 순서대로 시도한다. 시작 전 연결 실패는 재시도해도 안전하므로 지수 백오프로 다시 시도하고, 소진하면 다음 executor 로 넘긴다. 시작한 뒤에는 끝날 때까지 상태를 물어본다.
-    후보 = FAILOVER_ORDER(task)          // 배정 executor 우선, 헬스 기반이면 한가한 순
+같은 executor에 동일 task_id로 재시도한다. 접속 실패·429·503처럼 미접수가 확실한 경우에만 다른 후보로 넘긴다. 접수 여부가 불확실한 응답 유실과 폴링 장애에서는 자동 재배정하지 않는다. Executor는 보유 중인 task_id와 같은 본문의 재접수를 재실행 없이 처리하고, 다른 본문이면 409로 거절한다.
+    후보 = FAILOVER_ORDER(task)
     FOR url IN 후보:
-        TRY:
-            RETRY(최대 task_max_retries, 지수백오프):
-                POST url + "/tasks"  {task_id, job_id, sub_query, target_table, ...}
-            POLL(client, job, task)      // 아래 반복
-            RETURN                       // 종료 상태에 도달
-        CATCH 연결오류:
-            CONTINUE                     // 다음 executor 로 failover
-    task.status = FAILED
-    FUNCTION POLL(client, job, task):
-        transient = 0
-        WHILE task.status NOT IN (DONE, FAILED, CANCELLED):
-            IF CANCEL_OBSERVED(job) THEN task.status = CANCELLED; RETURN
-            SLEEP(설정.poll_interval_s)
-            TRY:
-                resp = GET url + "/tasks/" + task.task_id
-                transient = 0
-            CATCH 일시오류:
-                transient += 1
-                IF transient &gt; task_max_retries THEN RETHROW    // 상위가 failover 판단
-                CONTINUE
-            task.status = resp.status
-            task.rows_written / rows_read / current_phase / phases 갱신
+        접수불확실 = false
+        RETRY(최대 task_max_retries, 지수백오프):
+            TRY: POST url + "/tasks" {task_id, job_id, sub_query, target_table, ...}
+            CATCH 미접수가확실한오류: 다음 재시도
+            CATCH 응답유실등: 접수불확실 = true; 같은 url에서만 재시도
+            CATCH 요청충돌등: FAILED; RETURN
+        IF 접수실패 AND 접수불확실 THEN FAILED; RETURN
+        IF 접수실패 THEN 다음 후보
+        TRY: 종료 상태까지 같은 url에서 POLL
+        CATCH 폴링재시도소진: FAILED; RETURN
+        RETURN
+Task가 실패로 표시돼도 기존 실행이 끝났다는 보장은 없다. 대상 데이터와 실행 상태를 확인한 뒤 재처리한다.
 7. 배리어 뒤 2단계 적재(스테이징 모드만)
 _execute 가 돌아왔다는 것은 모든 조각이 종료 상태라는 뜻이며, 이것이 자연스러운 배리어가 된다. 그 뒤에 coordinator 가 중앙에서 2단계 적재를 수행한다. 다른 모드에서는 아무 일도 하지 않는다.
     RUN_STAGE_LOAD(job)     // local_stage: file:// 외부테이블 → staging → target
